--- a/data/trans_bre/P1_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,06</t>
+          <t>-0,85; 4,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,99</t>
+          <t>-1,04; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 3,42</t>
+          <t>-3,54; 3,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,44; -1,81</t>
+          <t>-11,49; -2,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 90,95</t>
+          <t>-14,69; 93,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 72,18</t>
+          <t>-10,09; 79,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 31,56</t>
+          <t>-25,07; 31,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,54; -8,37</t>
+          <t>-41,96; -8,97</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,5</t>
+          <t>-0,31; 4,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,28</t>
+          <t>-2,62; 2,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,45</t>
+          <t>-3,51; 2,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 10,29</t>
+          <t>-0,82; 9,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 105,15</t>
+          <t>-4,57; 99,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 35,57</t>
+          <t>-28,79; 35,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 26,22</t>
+          <t>-29,76; 26,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 145,93</t>
+          <t>-5,07; 132,41</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,73</t>
+          <t>-0,65; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,44</t>
+          <t>-2,64; 3,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 3,02</t>
+          <t>-4,6; 2,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -0,92</t>
+          <t>-12,71; -1,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 93,55</t>
+          <t>-7,56; 96,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 52,03</t>
+          <t>-27,29; 53,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 27,72</t>
+          <t>-29,79; 26,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-66,92; -7,46</t>
+          <t>-67,61; -9,8</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,01</t>
+          <t>-3,13; 2,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,59</t>
+          <t>0,49; 6,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,09; 6,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 6,16</t>
+          <t>-2,33; 5,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 23,54</t>
+          <t>-27,33; 31,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 80,22</t>
+          <t>4,52; 83,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 55,07</t>
+          <t>-0,14; 54,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 40,64</t>
+          <t>-11,37; 38,38</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,76</t>
+          <t>0,03; 2,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,96</t>
+          <t>0,26; 3,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,34</t>
+          <t>-1,05; 2,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,69</t>
+          <t>-3,66; 2,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 42,4</t>
+          <t>0,63; 42,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 38,39</t>
+          <t>3,2; 41,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 20,38</t>
+          <t>-7,64; 20,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 18,47</t>
+          <t>-20,14; 19,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,12</t>
+          <t>-4,84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-24,51%</t>
+          <t>-19,61%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,04</t>
+          <t>-1,01; 3,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,04</t>
+          <t>-0,85; 5,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,27</t>
+          <t>-4,13; 3,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -2,03</t>
+          <t>-8,99; -0,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 93,01</t>
+          <t>-17,33; 90,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 79,18</t>
+          <t>-10,37; 76,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 31,57</t>
+          <t>-28,09; 31,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,96; -8,97</t>
+          <t>-32,13; -2,83</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>-5,33%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,68</t>
+          <t>-0,31; 4,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,15</t>
+          <t>-2,37; 2,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,41</t>
+          <t>-3,2; 2,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,44</t>
+          <t>-3,72; 2,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 99,54</t>
+          <t>-4,1; 104,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 35,47</t>
+          <t>-27,61; 42,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 26,81</t>
+          <t>-27,41; 24,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 132,41</t>
+          <t>-20,03; 14,79</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-34,89%</t>
+          <t>-19,35%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 5,99</t>
+          <t>-0,45; 5,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,48</t>
+          <t>-2,28; 3,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,95</t>
+          <t>-4,36; 2,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,71; -1,43</t>
+          <t>-6,65; 0,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 96,32</t>
+          <t>-5,5; 92,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 53,06</t>
+          <t>-23,64; 63,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,79; 26,88</t>
+          <t>-29,45; 24,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-67,61; -9,8</t>
+          <t>-35,4; 2,49</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,63</t>
+          <t>-2,92; 2,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,53</t>
+          <t>0,6; 6,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 6,99</t>
+          <t>-0,02; 6,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,96</t>
+          <t>0,27; 6,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 31,94</t>
+          <t>-25,42; 31,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 83,81</t>
+          <t>4,81; 78,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 54,1</t>
+          <t>-0,07; 54,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 38,38</t>
+          <t>1,49; 42,37</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,08%</t>
+          <t>-4,51%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,73</t>
+          <t>0,07; 2,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,11</t>
+          <t>0,1; 2,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,43</t>
+          <t>-0,88; 2,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,82</t>
+          <t>-2,5; 0,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 42,5</t>
+          <t>0,89; 44,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 41,48</t>
+          <t>1,07; 39,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 20,78</t>
+          <t>-6,68; 20,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 19,67</t>
+          <t>-13,0; 4,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
